--- a/data/trans_orig/IP18A05-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP18A05-Clase-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3571</t>
+          <t>3232</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3984</t>
+          <t>3940</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,18%</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>90934</t>
+          <t>91273</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>176635</t>
+          <t>176679</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5634</t>
+          <t>4916</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2924</t>
+          <t>2442</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>483</t>
+          <t>481</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6057</t>
+          <t>6309</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>4,05%</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>74651</t>
+          <t>75369</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>72444</t>
+          <t>72926</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>149596</t>
+          <t>149344</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>155170</t>
+          <t>155172</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3590</t>
+          <t>4046</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6028</t>
+          <t>5631</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6351</t>
+          <t>7044</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>2,02%</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>168843</t>
+          <t>168387</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>170454</t>
+          <t>170851</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>342563</t>
+          <t>341870</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4862</t>
+          <t>4870</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4867</t>
+          <t>5279</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,81%</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>97838</t>
+          <t>97830</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>182961</t>
+          <t>182549</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7924</t>
+          <t>7758</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1183</t>
+          <t>1383</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>8191</t>
+          <t>8268</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3480</t>
+          <t>3319</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>13447</t>
+          <t>12394</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,07%</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>553286</t>
+          <t>553452</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>584337</t>
+          <t>584260</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>591345</t>
+          <t>591145</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,77%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1140291</t>
+          <t>1141344</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1150258</t>
+          <t>1150419</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,71%</t>
         </is>
       </c>
     </row>
@@ -3373,7 +3373,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4865</t>
+          <t>3865</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4059</t>
+          <t>3655</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3423,7 +3423,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3443,7 +3443,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5305</t>
+          <t>4493</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3458,7 +3458,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>2,68%</t>
         </is>
       </c>
     </row>
@@ -3481,7 +3481,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>76702</t>
+          <t>77702</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3516,7 +3516,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>81802</t>
+          <t>82206</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3551,7 +3551,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>162122</t>
+          <t>162934</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4972</t>
+          <t>5211</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5330</t>
+          <t>5093</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3801,7 +3801,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,88%</t>
         </is>
       </c>
     </row>
@@ -3859,7 +3859,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>82542</t>
+          <t>82303</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -3894,7 +3894,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>171604</t>
+          <t>171841</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -3909,7 +3909,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4094,7 +4094,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>5108</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4109,7 +4109,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4129,7 +4129,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4478</t>
+          <t>5068</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>3,1%</t>
         </is>
       </c>
     </row>
@@ -4202,7 +4202,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>77799</t>
+          <t>77890</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4237,7 +4237,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>159169</t>
+          <t>158579</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -4252,7 +4252,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>665</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6728</t>
+          <t>7176</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,47 +4412,47 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>3,74%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>2884</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>742</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>7124</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>1,34%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
           <t>0,34%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3,51%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>2884</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>742</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>7164</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,34%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2307</t>
+          <t>2645</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10230</t>
+          <t>10343</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>184941</t>
+          <t>184493</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>191017</t>
+          <t>191004</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,49 +4525,49 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
+          <t>99,65%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>301</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>212656</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>208416</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>214798</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>98,66%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>96,7%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
           <t>99,66%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>301</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>212656</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>208376</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>214798</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>98,66%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>96,68%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>99,66%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>575</t>
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>396979</t>
+          <t>396866</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>404902</t>
+          <t>404564</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,35%</t>
         </is>
       </c>
     </row>
@@ -4745,7 +4745,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3327</t>
+          <t>4343</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4780,7 +4780,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3237</t>
+          <t>2833</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4795,7 +4795,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4815,7 +4815,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4951</t>
+          <t>4983</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,85%</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>133638</t>
+          <t>132622</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -4888,7 +4888,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>129260</t>
+          <t>129664</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -4903,7 +4903,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -4923,7 +4923,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>264512</t>
+          <t>264480</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -4938,7 +4938,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -5088,7 +5088,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4513</t>
+          <t>3898</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5123,7 +5123,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4174</t>
+          <t>3539</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5158,7 +5158,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4576</t>
+          <t>5777</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5173,7 +5173,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>4,73%</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>48147</t>
+          <t>48762</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>91,43%</t>
+          <t>92,6%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5231,7 +5231,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>65336</t>
+          <t>65971</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>94,91%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5266,7 +5266,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>117593</t>
+          <t>116392</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2108</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9282</t>
+          <t>9795</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>3805</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>13590</t>
+          <t>13142</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>7641</t>
+          <t>7638</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>19972</t>
+          <t>18959</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>623648</t>
+          <t>623135</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>630917</t>
+          <t>630822</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,67%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>660329</t>
+          <t>660777</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>670266</t>
+          <t>670114</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1286878</t>
+          <t>1287891</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1299209</t>
+          <t>1299212</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,7 +5624,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -6008,7 +6008,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3302</t>
+          <t>3308</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6023,7 +6023,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6043,7 +6043,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6909</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6078,7 +6078,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6457</t>
+          <t>6255</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6093,7 +6093,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,72%</t>
         </is>
       </c>
     </row>
@@ -6116,7 +6116,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>72044</t>
+          <t>72038</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6151,7 +6151,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>86042</t>
+          <t>87984</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6186,7 +6186,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>161840</t>
+          <t>162042</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -6351,7 +6351,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2480</t>
+          <t>2973</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6366,7 +6366,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>5469</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>553</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5459</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6436,7 +6436,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>3,22%</t>
         </is>
       </c>
     </row>
@@ -6459,7 +6459,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>93951</t>
+          <t>93458</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -6474,7 +6474,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -6494,7 +6494,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>93366</t>
+          <t>93135</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -6509,7 +6509,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>189575</t>
+          <t>188749</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>194485</t>
+          <t>194481</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,7 +6544,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>650</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>7222</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>933</t>
+          <t>1086</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8773</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2802</t>
+          <t>2354</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11778</t>
+          <t>12139</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,08%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>198357</t>
+          <t>198241</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>204859</t>
+          <t>204813</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,68%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>179683</t>
+          <t>180185</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>187523</t>
+          <t>187370</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>382141</t>
+          <t>381780</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>391117</t>
+          <t>391565</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,4%</t>
         </is>
       </c>
     </row>
@@ -7415,7 +7415,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4680</t>
+          <t>4782</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7430,7 +7430,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7450,7 +7450,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4937</t>
+          <t>4586</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7465,7 +7465,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,83%</t>
         </is>
       </c>
     </row>
@@ -7523,7 +7523,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>122828</t>
+          <t>122726</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -7538,7 +7538,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -7558,7 +7558,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>245213</t>
+          <t>245564</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -7573,7 +7573,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>599</t>
+          <t>596</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5107</t>
+          <t>5001</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7758,7 +7758,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4186</t>
+          <t>4179</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7773,7 +7773,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1244</t>
+          <t>1258</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7086</t>
+          <t>7243</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,18%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>51201</t>
+          <t>51307</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>55709</t>
+          <t>55712</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,93%</t>
+          <t>91,12%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -7866,7 +7866,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>56779</t>
+          <t>56786</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -7881,7 +7881,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>110187</t>
+          <t>110030</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>116029</t>
+          <t>116015</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,93%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2466</t>
+          <t>2535</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>10579</t>
+          <t>10658</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4442</t>
+          <t>4390</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>15216</t>
+          <t>14898</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>8710</t>
+          <t>8328</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>22026</t>
+          <t>22209</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,78%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>598555</t>
+          <t>598476</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>606668</t>
+          <t>606599</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,58%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>620772</t>
+          <t>621090</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>631546</t>
+          <t>631598</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1223096</t>
+          <t>1222913</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1236412</t>
+          <t>1236794</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,33%</t>
         </is>
       </c>
     </row>
@@ -8643,7 +8643,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3163</t>
+          <t>2738</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8658,7 +8658,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8678,7 +8678,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>3212</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8693,7 +8693,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>403</t>
+          <t>426</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4790</t>
+          <t>4297</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>9,48%</t>
         </is>
       </c>
     </row>
@@ -8751,7 +8751,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>21610</t>
+          <t>22035</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -8766,7 +8766,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,23%</t>
+          <t>88,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -8786,7 +8786,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17364</t>
+          <t>17326</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -8801,7 +8801,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,55%</t>
+          <t>84,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>40521</t>
+          <t>41014</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>44908</t>
+          <t>44885</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,43%</t>
+          <t>90,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,06%</t>
         </is>
       </c>
     </row>
@@ -9021,7 +9021,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6633</t>
+          <t>5640</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9036,7 +9036,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>40,95%</t>
+          <t>34,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9056,7 +9056,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6944</t>
+          <t>7371</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9071,7 +9071,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>27,62%</t>
         </is>
       </c>
     </row>
@@ -9129,7 +9129,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>9563</t>
+          <t>10556</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -9144,7 +9144,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>59,05%</t>
+          <t>65,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -9164,7 +9164,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>19743</t>
+          <t>19316</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -9179,7 +9179,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,98%</t>
+          <t>72,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>572</t>
+          <t>531</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5293</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9707,7 +9707,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3168</t>
+          <t>3377</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9722,7 +9722,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1017</t>
+          <t>826</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6435</t>
+          <t>6307</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>8,84%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>24909</t>
+          <t>24850</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>29630</t>
+          <t>29671</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,48%</t>
+          <t>82,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>37962</t>
+          <t>37753</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -9830,7 +9830,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,3%</t>
+          <t>91,79%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>64897</t>
+          <t>65025</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>70315</t>
+          <t>70506</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,98%</t>
+          <t>91,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,84%</t>
         </is>
       </c>
     </row>
@@ -10393,7 +10393,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5502</t>
+          <t>5507</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10408,7 +10408,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>47,14%</t>
+          <t>47,18%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10428,7 +10428,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5771</t>
+          <t>5870</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10443,7 +10443,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>27,91%</t>
         </is>
       </c>
     </row>
@@ -10501,7 +10501,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>6169</t>
+          <t>6164</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -10516,7 +10516,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>52,86%</t>
+          <t>52,82%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -10536,7 +10536,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>15257</t>
+          <t>15158</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -10551,7 +10551,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>72,55%</t>
+          <t>72,09%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1035</t>
+          <t>1041</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6687</t>
+          <t>6697</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1824</t>
+          <t>1999</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>11015</t>
+          <t>10422</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3950</t>
+          <t>4351</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>13934</t>
+          <t>15388</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,72%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>91992</t>
+          <t>91982</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>97644</t>
+          <t>97638</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>119347</t>
+          <t>119940</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>128538</t>
+          <t>128363</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>92,01%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>215108</t>
+          <t>213654</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>225092</t>
+          <t>224691</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>93,28%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,1%</t>
         </is>
       </c>
     </row>
